--- a/DocumentUnderstandingProcess/contentFiles/any/any/pt0/VisualBasic/Tests/Cache/ExportMergedDocuments_2-2.xlsx
+++ b/DocumentUnderstandingProcess/contentFiles/any/any/pt0/VisualBasic/Tests/Cache/ExportMergedDocuments_2-2.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:si>
     <x:t>Name</x:t>
   </x:si>
